--- a/output/第10期計画_所得段階別第1号被保険者数の将来推計.xlsx
+++ b/output/第10期計画_所得段階別第1号被保険者数の将来推計.xlsx
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="C9" s="23" t="n">
-        <v>6436.66</v>
+        <v>6438.83</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>6436.09</v>
+        <v>6438.26</v>
       </c>
       <c r="E9" s="23" t="n">
         <v>0.57</v>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>6436.66円 対 6436.09円（差0.57円）</t>
+          <t>6438.83円 対 6438.26円（差0.57円）</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">

--- a/output/第10期計画_所得段階別第1号被保険者数の将来推計.xlsx
+++ b/output/第10期計画_所得段階別第1号被保険者数の将来推計.xlsx
@@ -593,7 +593,7 @@
         <is>
           <t>【要点】
 ・構成比は令和6年度の実績で固定しました。当方の保険料算定が採用している係数（0.991352）と同じであり、見える化システムが本表の人数から算定する補正後被保険者数が当方の値と一致するためです。
-・構成比を令和7年度に改めると係数は1.015890となり、算定上の月額が163円下がります。これは段階別人数の作り方の問題ではなく、係数をどの年度で置くかという既存の選択です（将来推計 第3段階 04シート）。
+・構成比を令和7年度に改めると係数は1.015890となり、算定上の月額が▲156円動きます。これは段階別人数の作り方の問題ではなく、係数をどの年度で置くかという既存の選択です（将来推計 第3段階 04シート、本表の04シート）。
 ・当連合の所得段階は16段階です（第9期の条例。第13段階を多段階化）。見える化システムの標準は13段階であるため、入力画面では所得段階の設定を「弾力化」とします。
 ・第10期の段階数・乗率は政令改正により変わり得ます（確認事項No.33）。本表は第9期の16段階・乗率をそのまま用いた暫定の値です。</t>
         </is>
@@ -991,7 +991,7 @@
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>-163円</t>
+          <t>▲156円</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>+154円</t>
+          <t>＋147円</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -1030,8 +1030,8 @@
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>注1）本表は令和6年度の構成比を採ります。当方の保険料算定の基本ケースと同じ係数であり、段階別の人数を入れたときにシステムが出す補正後被保険者数が当方の値と一致します。
-注2）月額への効きは、給付費・地域支援事業費など他の前提をすべて同じにしたうえで係数だけを置き換えた場合の差です（基本ケース6740円に対する差）。
-注3）構成比を令和7年度に改めるかどうかは、本表の作り方ではなく係数の選択そのものです。将来推計 第3段階 04シートの感度として既に掲げています。</t>
+注2）月額への効きは、給付費・地域支援事業費など他の前提をすべて同じにしたうえで係数だけを置き換えた場合の差です。差の基準は本計画の算定上の月額基準額6438.26円（サービス見込量の算定による）であり、基準が変われば差の額も変わります。
+注3）構成比を令和7年度に改めるかどうかは、本表の作り方ではなく係数の選択そのものです。将来推計 第3段階 04シート及び計画素案 第6章第6節の感度として掲げています。</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>-163円</t>
+          <t>-156円</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
